--- a/PMD1_15_Casos_Sinteticos/11_Retail_PMD1.xlsx
+++ b/PMD1_15_Casos_Sinteticos/11_Retail_PMD1.xlsx
@@ -18862,7 +18862,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Cliente 1</t>
+          <t>Raúl Delgado Soto</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -18882,7 +18882,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Cliente 2</t>
+          <t>Valeria Ríos Vargas</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -18902,7 +18902,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cliente 3</t>
+          <t>Andrés Benites Aguilar</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -18922,7 +18922,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cliente 4</t>
+          <t>Claudia Castillo Reyes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -18942,7 +18942,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cliente 5</t>
+          <t>Víctor Ccori Chávez</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -18962,7 +18962,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cliente 6</t>
+          <t>Diana Condori Mamani</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -18982,7 +18982,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Cliente 7</t>
+          <t>Óscar Reyes Quispe</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -19002,7 +19002,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Cliente 8</t>
+          <t>Ana Vargas Ccori</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -19022,7 +19022,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Cliente 9</t>
+          <t>Luis Paredes Soto</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -19042,7 +19042,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cliente 10</t>
+          <t>María Mamani Vargas</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -19062,7 +19062,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Cliente 11</t>
+          <t>Jorge Campos Aguilar</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -19082,7 +19082,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cliente 12</t>
+          <t>Rosa Rojas Reyes</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -19102,7 +19102,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cliente 13</t>
+          <t>Carlos Gutiérrez Chávez</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -19122,7 +19122,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Cliente 14</t>
+          <t>Lucía Cárdenas Mamani</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -19142,7 +19142,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Cliente 15</t>
+          <t>Miguel Soto Quispe</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -19162,7 +19162,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Cliente 16</t>
+          <t>Carmen Flores Salazar</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -19182,7 +19182,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Cliente 17</t>
+          <t>José Chávez Ríos</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -19202,7 +19202,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Cliente 18</t>
+          <t>Patricia Delgado Rojas</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -19222,7 +19222,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cliente 19  </t>
+          <t xml:space="preserve">Diego Ríos Espinoza  </t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -19242,7 +19242,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Cliente 20</t>
+          <t>Milagros Benites Cruz</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -19262,7 +19262,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Cliente 21</t>
+          <t>Gabriela Ccori Cárdenas</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -19282,7 +19282,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Cliente 22</t>
+          <t>Hugo Condori Gómez</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -19302,7 +19302,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Cliente 23</t>
+          <t>Fiorella Reyes Ramírez</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -19322,7 +19322,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Cliente 24</t>
+          <t>César Mendoza Condori</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -19342,7 +19342,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Cliente 25</t>
+          <t>Paola Salazar Flores</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -19362,7 +19362,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Cliente 26</t>
+          <t>Iván Valdivia Paredes</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -19382,7 +19382,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Cliente 27</t>
+          <t>Sofía Cruz Navarro</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -19402,7 +19402,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Cliente 28</t>
+          <t>Martín Huamán Mendoza</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -19422,7 +19422,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Cliente 29</t>
+          <t>Elena Ramírez Delgado</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -19442,7 +19442,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Cliente 30</t>
+          <t>Raúl Aguilar Campos</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -19462,7 +19462,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Cliente 31</t>
+          <t>Valeria Navarro Torres</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -19482,7 +19482,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Cliente 32</t>
+          <t>Andrés Quispe Valdivia</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -19502,7 +19502,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Cliente 33</t>
+          <t>Claudia Torres Benites</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -19522,7 +19522,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Cliente 34</t>
+          <t>Víctor Espinoza Gutiérrez</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -19542,7 +19542,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Cliente 35</t>
+          <t>Óscar Gómez Huamán</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -19562,7 +19562,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Cliente 36</t>
+          <t>Ana Castillo Delgado</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -19582,7 +19582,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Cliente 37</t>
+          <t>Luis Ccori Campos</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -19602,7 +19602,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cliente 38  </t>
+          <t xml:space="preserve">María Condori Torres  </t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -19622,7 +19622,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Cliente 39</t>
+          <t>Jorge Reyes Valdivia</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -19642,7 +19642,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Cliente 40</t>
+          <t>Rosa Mendoza Benites</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -19662,7 +19662,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Cliente 41</t>
+          <t>Carlos Salazar Gutiérrez</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -19682,7 +19682,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Cliente 42</t>
+          <t>Lucía Valdivia Poma</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -19702,7 +19702,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Cliente 43</t>
+          <t>Miguel Cruz Huamán</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -19722,7 +19722,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Cliente 44</t>
+          <t>Carmen Huamán Ccori</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -19742,7 +19742,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Cliente 45</t>
+          <t>José Ramírez Soto</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -19762,7 +19762,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Cliente 46</t>
+          <t>Patricia Aguilar Vargas</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -19782,7 +19782,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Cliente 47</t>
+          <t>Diego Navarro Aguilar</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -19802,7 +19802,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Cliente 48</t>
+          <t>Milagros Quispe Reyes</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -19822,7 +19822,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Cliente 49</t>
+          <t>Renzo Torres Chávez</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -19842,7 +19842,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Cliente 50</t>
+          <t>Gabriela Espinoza Mamani</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -19862,7 +19862,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Cliente 51</t>
+          <t>Hugo Poma Quispe</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -19882,7 +19882,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Cliente 52</t>
+          <t>Fiorella Gómez Salazar</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -19902,7 +19902,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Cliente 53</t>
+          <t>César Vargas Ríos</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -19922,7 +19922,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Cliente 54</t>
+          <t>Paola Paredes Rojas</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -19942,7 +19942,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Cliente 55</t>
+          <t>Iván Mamani Espinoza</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -19962,7 +19962,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Cliente 56</t>
+          <t>Sofía Campos Cruz</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -19982,7 +19982,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cliente 57  </t>
+          <t xml:space="preserve">Martín Rojas Castillo  </t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -20002,7 +20002,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Cliente 58</t>
+          <t>Elena Gutiérrez Cárdenas</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -20022,7 +20022,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Cliente 59</t>
+          <t>Raúl Cárdenas Gómez</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -20042,7 +20042,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Cliente 60</t>
+          <t>Valeria Soto Ramírez</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -20062,7 +20062,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Cliente 61</t>
+          <t>Andrés Flores Condori</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -20082,7 +20082,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Cliente 62</t>
+          <t>Claudia Chávez Flores</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -20102,7 +20102,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Cliente 63</t>
+          <t>Víctor Delgado Paredes</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -20122,7 +20122,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Cliente 64</t>
+          <t>Diana Ríos Navarro</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -20142,7 +20142,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Cliente 65</t>
+          <t>Óscar Benites Mendoza</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -20162,7 +20162,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Cliente 66</t>
+          <t>Ana Torres Cárdenas</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -20182,7 +20182,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Cliente 67</t>
+          <t>Luis Espinoza Gómez</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -20202,7 +20202,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Cliente 68</t>
+          <t>María Poma Ramírez</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -20222,7 +20222,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Cliente 69</t>
+          <t>Jorge Gómez Condori</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -20242,7 +20242,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Cliente 70</t>
+          <t>Rosa Vargas Flores</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -20262,7 +20262,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Cliente 71</t>
+          <t>Lucía Mamani Navarro</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -20282,7 +20282,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Cliente 72</t>
+          <t>Miguel Campos Mendoza</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -20302,7 +20302,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Cliente 73</t>
+          <t>Carmen Rojas Delgado</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -20322,7 +20322,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Cliente 74</t>
+          <t>José Gutiérrez Campos</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -20342,7 +20342,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Cliente 75</t>
+          <t>Patricia Cárdenas Torres</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -20362,7 +20362,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cliente 76  </t>
+          <t xml:space="preserve">Diego Soto Valdivia  </t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -20382,7 +20382,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Cliente 77</t>
+          <t>Milagros Flores Benites</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -20402,7 +20402,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Cliente 78</t>
+          <t>Renzo Chávez Gutiérrez</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -20422,7 +20422,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Cliente 79</t>
+          <t>Gabriela Delgado Poma</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -20442,7 +20442,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Cliente 80</t>
+          <t>Hugo Ríos Huamán</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -20462,7 +20462,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Cliente 81</t>
+          <t>Fiorella Benites Ccori</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -20482,7 +20482,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Cliente 82</t>
+          <t>César Castillo Soto</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -20502,7 +20502,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Cliente 83</t>
+          <t>Paola Ccori Vargas</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -20522,7 +20522,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Cliente 84</t>
+          <t>Iván Condori Aguilar</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -20542,7 +20542,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Cliente 85</t>
+          <t>Martín Mendoza Chávez</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -20562,7 +20562,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Cliente 86</t>
+          <t>Elena Salazar Mamani</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -20582,7 +20582,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Cliente 87</t>
+          <t>Raúl Valdivia Quispe</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -20602,7 +20602,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Cliente 88</t>
+          <t>Valeria Cruz Salazar</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -20622,7 +20622,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Cliente 89</t>
+          <t>Andrés Huamán Ríos</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -20642,7 +20642,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Cliente 90</t>
+          <t>Claudia Ramírez Rojas</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -20662,7 +20662,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Cliente 91</t>
+          <t>Víctor Aguilar Espinoza</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -20682,7 +20682,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Cliente 92</t>
+          <t>Diana Navarro Cruz</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -20702,7 +20702,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Cliente 93</t>
+          <t>Óscar Quispe Castillo</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -20722,7 +20722,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Cliente 94</t>
+          <t>Ana Chávez Mamani</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -20742,7 +20742,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cliente 95  </t>
+          <t xml:space="preserve">Luis Delgado Quispe  </t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -20762,7 +20762,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Cliente 96</t>
+          <t>María Ríos Salazar</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -20782,7 +20782,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Cliente 97</t>
+          <t>Jorge Benites Ríos</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -20802,7 +20802,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Cliente 98</t>
+          <t>Rosa Castillo Rojas</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -20822,7 +20822,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Cliente 99</t>
+          <t>Carlos Ccori Espinoza</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -20842,7 +20842,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Cliente 100</t>
+          <t>Lucía Condori Cruz</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -20862,7 +20862,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Cliente 101</t>
+          <t>Miguel Reyes Castillo</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -20882,7 +20882,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Cliente 102</t>
+          <t>Carmen Mendoza Cárdenas</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -20902,7 +20902,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Cliente 103</t>
+          <t>José Salazar Gómez</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -20922,7 +20922,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Cliente 104</t>
+          <t>Patricia Valdivia Ramírez</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -20942,7 +20942,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Cliente 105</t>
+          <t>Diego Cruz Condori</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -20962,7 +20962,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Cliente 106</t>
+          <t>Milagros Huamán Flores</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -20982,7 +20982,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Cliente 107</t>
+          <t>Renzo Ramírez Paredes</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -21002,7 +21002,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Cliente 108</t>
+          <t>Gabriela Aguilar Navarro</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -21022,7 +21022,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Cliente 109</t>
+          <t>Hugo Navarro Mendoza</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -21042,7 +21042,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Cliente 110</t>
+          <t>Fiorella Quispe Delgado</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -21062,7 +21062,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Cliente 111</t>
+          <t>César Torres Campos</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -21082,7 +21082,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Cliente 112</t>
+          <t>Paola Espinoza Torres</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -21102,7 +21102,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Cliente 113</t>
+          <t>Iván Poma Valdivia</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -21122,7 +21122,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cliente 114  </t>
+          <t xml:space="preserve">Sofía Gómez Benites  </t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -21142,7 +21142,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Cliente 115</t>
+          <t>Martín Vargas Gutiérrez</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -21162,7 +21162,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Cliente 116</t>
+          <t>Elena Paredes Poma</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -21182,7 +21182,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Cliente 117</t>
+          <t>Raúl Mamani Huamán</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -21202,7 +21202,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Cliente 118</t>
+          <t>Valeria Campos Ccori</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -21222,7 +21222,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Cliente 119</t>
+          <t>Andrés Rojas Soto</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -21242,7 +21242,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Cliente 120</t>
+          <t>Claudia Gutiérrez Vargas</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -21304,7 +21304,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>pantalon 1</t>
+          <t>Jean skinny</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -21324,7 +21324,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>zapatilla 2</t>
+          <t>Zapatillas urbanas blancas</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -21344,7 +21344,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>accesorio 3</t>
+          <t>Gorra</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -21364,7 +21364,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>accesorio 4</t>
+          <t>Correa de cuero</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -21384,7 +21384,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>zapatilla 5</t>
+          <t>Zapatillas running</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -21404,7 +21404,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>accesorio 6</t>
+          <t>Mochila urbana</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -21424,7 +21424,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>pantalon 7</t>
+          <t>Pantalón chino</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -21444,7 +21444,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>accesorio 8</t>
+          <t>Billetera</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -21464,7 +21464,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>zapatilla 9</t>
+          <t>Zapatillas de lona</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -21484,7 +21484,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>accesorio 10</t>
+          <t>Lentes de sol</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -21504,7 +21504,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>polo 11</t>
+          <t>Polo básico de algodón pima</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -21524,7 +21524,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>zapatilla 12</t>
+          <t>Zapatillas de skate</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -21544,7 +21544,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>accesorio 13</t>
+          <t>Bufanda de alpaca</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -21564,7 +21564,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>polo 14</t>
+          <t>Polo estampado</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -21584,7 +21584,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>pantalon 15</t>
+          <t>Jean clásico</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -21604,7 +21604,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>casaca 16</t>
+          <t>Casaca de jean</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -21624,7 +21624,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>pantalon 17</t>
+          <t>Pantalón de vestir</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -21644,7 +21644,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>pantalon 18</t>
+          <t>Jogger</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -21664,7 +21664,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>pantalon 19</t>
+          <t>Pantalón cargo</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -21684,7 +21684,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>zapatilla 20</t>
+          <t>Zapatillas para training</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -21740,7 +21740,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Retail sede 1</t>
+          <t>Moda Urbana Los Olivos</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -21757,7 +21757,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Retail sede 2</t>
+          <t>Moda Urbana La Molina</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -21774,7 +21774,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Retail sede 3</t>
+          <t>Moda Urbana Surco</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -21791,7 +21791,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Retail sede 4</t>
+          <t>Moda Urbana San Miguel</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -21808,7 +21808,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Retail sede 5</t>
+          <t>Moda Urbana Chorrillos</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
